--- a/Beyomo_Changes_List_Updated.xlsx
+++ b/Beyomo_Changes_List_Updated.xlsx
@@ -566,12 +566,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Swipe-to-confirm actions - Slide to accept, start and complete a job instead of tapping a button.</t>
+          <t xml:space="preserve">Booking modal amounts synchronized - Adding or removing services immediately updates Base Amount, Tax and Total Amount using the saved backend calculations, without closing and reopening the modal; existing tax rules and total behavior are preserved.</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start Service OTP - Job can only be started after entering the customer's 4-digit code.</t>
+          <t xml:space="preserve">Blank screen after booking service changes fixed - Saved bookings and detail refreshes retain the service name as text, and null/non-array service or package JSON is normalized to an empty list, preventing rendering and list-operation crashes; confirmed working on the live dashboard.</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UPI QR for payment collection - QR shown on completion so the customer can scan and pay with any UPI app.</t>
+          <t xml:space="preserve">Create bookings on behalf of customers - Search and select an existing customer, or create a customer profile from the booking form before selecting services and placing the booking.</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settlement History screen (new) - Every past settlement with date, time, amount, method and reference.</t>
+          <t xml:space="preserve">Map-based service address selection - Choose a saved customer address or add a new address using location search and a map; the selected address determines the service city and available catalog.</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outstanding balance on Earnings - Now always matches the settlement screen figure.</t>
+          <t xml:space="preserve">Combined service and package cart for admin bookings - Add individual services, custom add-ons, fixed combos and flexible packages together, select eligible package services and adjust package quantities from one to five.</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank details in Edit Profile - Partner can add or update account holder, bank name, account number and IFSC, with validation.</t>
+          <t xml:space="preserve">Review Total before creating admin bookings - Shows the server-calculated subtotal, coupon discount, GST and final total, supports eligible offers, and requires another review if the order or price changes; validates city availability and the minimum booking amount.</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Suspended screen (new) - If admin suspends a partner, the app detects it and blocks use; access returns automatically once reactivated.</t>
+          <t xml:space="preserve">Booking status controls - Admin can move bookings between supported statuses, including restoring a cancelled booking to In Progress; service statuses and completion details update with the booking status.</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner App</t>
+          <t xml:space="preserve">Admin Dashboard</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accurate Online / Offline availability - No longer shows 'You are Online' on launch by mistake; goes offline automatically if the app is closed or loses signal.</t>
+          <t xml:space="preserve">Created by Admin booking label - Booking lists and details identify bookings created by an administrator.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live available-jobs count - The New Booking count updates the moment availability is switched on or off.</t>
+          <t xml:space="preserve">Swipe-to-confirm actions - Slide to accept, start and complete a job instead of tapping a button.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notification sound and banner alerts - Booking notifications play a custom sound and appear as a heads-up banner even while the app is open.</t>
+          <t xml:space="preserve">Start Service OTP - Job can only be started after entering the customer's 4-digit code.</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notification list working and cleared on logout - The bell list now loads, and one partner's notifications never carry over to the next login.</t>
+          <t xml:space="preserve">UPI QR for payment collection - QR shown on completion so the customer can scan and pay with any UPI app.</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">City selection remembered - The partner's saved city is pre-selected when reopening the screen.</t>
+          <t xml:space="preserve">Settlement History screen (new) - Every past settlement with date, time, amount, method and reference.</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back button after logout - Cannot walk back into the previous partner's session.</t>
+          <t xml:space="preserve">Outstanding balance on Earnings - Now always matches the settlement screen figure.</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whole-rupee amounts across all screens - All earnings and job amounts shown in whole rupees.</t>
+          <t xml:space="preserve">Bank details in Edit Profile - Partner can add or update account holder, bank name, account number and IFSC, with validation.</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival, OTP verification and service start flow - Swipe Reached to Customer Location to open the checklist and customer OTP prompt; verifying the code unlocks a separate Start Service swipe.</t>
+          <t xml:space="preserve">Account Suspended screen (new) - If admin suspends a partner, the app detects it and blocks use; access returns automatically once reactivated.</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reopen customer OTP verification - If the OTP sheet is dismissed, Verify Customer OTP opens it again; the sheet adjusts for the keyboard and can be closed by tapping outside.</t>
+          <t xml:space="preserve">Accurate Online / Offline availability - No longer shows 'You are Online' on launch by mistake; goes offline automatically if the app is closed or loses signal.</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">iOS swipe gesture fixes - Confirmation swipes work with iOS navigation gestures; the embedded arrival swipe temporarily pauses parent scrolling while dragging.</t>
+          <t xml:space="preserve">Live available-jobs count - The New Booking count updates the moment availability is switched on or off.</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add combos and packages from the checklist - Separate tabs allow fixed combos and flexible packages to be added, including choosing the required number of services for a flexible package.</t>
+          <t xml:space="preserve">Notification sound and banner alerts - Booking notifications play a custom sound and appear as a heads-up banner even while the app is open.</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove checklist services at quantity one - The minus control becomes a delete icon when only one item remains; the catalog selection can also be cleared at quantity one.</t>
+          <t xml:space="preserve">Notification list working and cleared on logout - The bell list now loads, and one partner's notifications never carry over to the next login.</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offer pricing on partner services - Catalog selections and checklist/active-job services show valid offer prices, original prices and discount percentages, with totals calculated from the offer price.</t>
+          <t xml:space="preserve">City selection remembered - The partner's saved city is pre-selected when reopening the screen.</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed offers on partner-added services - Checklist and active-job screens recheck offers and restore normal prices for affected partner-added services, update booking totals and notify the partner before continuing.</t>
+          <t xml:space="preserve">Back button after logout - Cannot walk back into the previous partner's session.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service catalog retry in checklist - Loading errors show a clear message and Retry action instead of leaving an empty service picker.</t>
+          <t xml:space="preserve">Whole-rupee amounts across all screens - All earnings and job amounts shown in whole rupees.</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed-service labels in job details - Services removed from a job display a Removed badge alongside the existing Added label for partner additions.</t>
+          <t xml:space="preserve">Arrival, OTP verification and service start flow - Swipe Reached to Customer Location to open the checklist and customer OTP prompt; verifying the code unlocks a separate Start Service swipe.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner login and approval navigation reset - Successful login and entry after approval clear the previous login/OTP/account-status navigation history.</t>
+          <t xml:space="preserve">Reopen customer OTP verification - If the OTP sheet is dismissed, Verify Customer OTP opens it again; the sheet adjusts for the keyboard and can be closed by tapping outside.</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner login OTP keyboard handling - The OTP screen scrolls and adjusts to the keyboard so verification controls remain accessible.</t>
+          <t xml:space="preserve">iOS swipe gesture fixes - Confirmation swipes work with iOS navigation gestures; the embedded arrival swipe temporarily pauses parent scrolling while dragging.</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Availability toggle refresh race fixed - Dashboard polling respects an in-progress availability change, and foreground handling reads the latest online state.</t>
+          <t xml:space="preserve">Add combos and packages from the checklist - Separate tabs allow fixed combos and flexible packages to be added, including choosing the required number of services for a flexible package.</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pay-first booking flow - Payment is completed before the booking is created, so a cancelled or failed payment never leaves a stuck booking.</t>
+          <t xml:space="preserve">Remove checklist services at quantity one - The minus control becomes a delete icon when only one item remains; the catalog selection can also be cleared at quantity one.</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service start code on booking details - The 4-digit code the customer shares with the expert to start the service.</t>
+          <t xml:space="preserve">Offer pricing on partner services - Catalog selections and checklist/active-job services show valid offer prices, original prices and discount percentages, with totals calculated from the offer price.</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full bill breakdown on booking details - Item-wise charges, taxes, discount and total, so the paid amount is fully explained.</t>
+          <t xml:space="preserve">Removed offers on partner-added services - Checklist and active-job screens recheck offers and restore normal prices for affected partner-added services, update booking totals and notify the partner before continuing.</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reschedule details on booking - Shows that a booking was rescheduled and the original slot.</t>
+          <t xml:space="preserve">Service catalog retry in checklist - Loading errors show a clear message and Retry action instead of leaving an empty service picker.</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subcategory filter chips in service listing - For example Waxing - Honey / Rica / Brazilian / Roll-on.</t>
+          <t xml:space="preserve">Removed-service labels in job details - Services removed from a job display a Removed badge alongside the existing Added label for partner additions.</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cart shared across categories - Selections from different categories stay together, and the back button no longer wipes the cart.</t>
+          <t xml:space="preserve">Partner login and approval navigation reset - Successful login and entry after approval clear the previous login/OTP/account-status navigation history.</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">City-wise services and pricing - Only services offered in the selected city are shown, at that city's price.</t>
+          <t xml:space="preserve">Partner login OTP keyboard handling - The OTP screen scrolls and adjusts to the keyboard so verification controls remain accessible.</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change-city confirmation - Warns before clearing the cart when switching to another city.</t>
+          <t xml:space="preserve">Availability toggle refresh race fixed - Dashboard polling respects an in-progress availability change, and foreground handling reads the latest online state.</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saved city checked on launch - If the saved city is no longer served, the app re-detects instead of getting stuck.</t>
+          <t xml:space="preserve">Notification taps open the relevant job - Available-booking alerts open the incoming request or available list; assigned-job updates open Job Details or Active Job based on status. Taps wait for startup/login to finish and duplicate taps are ignored.</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer App</t>
+          <t xml:space="preserve">Partner App</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Improved location and address picker - Better GPS accuracy, map opens on the last known location, and correct town/locality names in the address form.</t>
+          <t xml:space="preserve">Partner Android build version updated - Current versionName is 1.1.6 and versionCode is 16.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">OTP autofill on Android - The SMS code appears above the keyboard and verifies automatically once filled.</t>
+          <t xml:space="preserve">Pay-first booking flow - Payment is completed before the booking is created, so a cancelled or failed payment never leaves a stuck booking.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back button after login / signup - Can no longer return to the OTP or phone-number screen from inside the app.</t>
+          <t xml:space="preserve">Service start code on booking details - The 4-digit code the customer shares with the expert to start the service.</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keyboard no longer covers the bottom bar - The tab bar and cart bar hide while typing.</t>
+          <t xml:space="preserve">Full bill breakdown on booking details - Item-wise charges, taxes, discount and total, so the paid amount is fully explained.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home screen logo centred correctly - The logo now sits in the true middle of the header whatever the city name is.</t>
+          <t xml:space="preserve">Reschedule details on booking - Shows that a booking was rescheduled and the original slot.</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whole-rupee amounts across all screens - All prices and totals shown in whole rupees.</t>
+          <t xml:space="preserve">Subcategory filter chips in service listing - For example Waxing - Honey / Rica / Brazilian / Roll-on.</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cart shortcut in bottom navigation - Open checkout directly from the Cart button, with a badge showing the number of selected items.</t>
+          <t xml:space="preserve">Cart shared across categories - Selections from different categories stay together, and the back button no longer wipes the cart.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Services, combos and packages in one cart - Checkout handles multiple packages and individual services together, with independent package quantities and correctly calculated extras.</t>
+          <t xml:space="preserve">City-wise services and pricing - Only services offered in the selected city are shown, at that city's price.</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add More Services from checkout - Returns to Home so customers can add services, combos or packages and come back with their selections retained.</t>
+          <t xml:space="preserve">Change-city confirmation - Warns before clearing the cart when switching to another city.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checkout state reset for a different package - Reopening checkout with another package refreshes its services, quantities and offer state instead of retaining the previous package selections.</t>
+          <t xml:space="preserve">Saved city checked on launch - If the saved city is no longer served, the app re-detects instead of getting stuck.</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service offer prices throughout the app - Home cards, service lists, cart, checkout and booking details show the discounted price, crossed-out original price and percentage off.</t>
+          <t xml:space="preserve">Improved location and address picker - Better GPS accuracy, map opens on the last known location, and correct town/locality names in the address form.</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed service offers refresh automatically - Service screens and checkout recheck offers, restore normal prices and update cart totals with an in-app notice when an offer is no longer available; prices are checked again before payment.</t>
+          <t xml:space="preserve">OTP autofill on Android - The SMS code appears above the keyboard and verifies automatically once filled.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Free-service offer eligibility rechecked - Removing qualifying paid services clears an ineligible free item; eligibility is checked again before booking submission.</t>
+          <t xml:space="preserve">Back button after login / signup - Can no longer return to the OTP or phone-number screen from inside the app.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Download and view booking invoices - Generates a PDF invoice from booking data, saves it on the device and provides a View Invoice action with clear success or failure feedback.</t>
+          <t xml:space="preserve">Keyboard no longer covers the bottom bar - The tab bar and cart bar hide while typing.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Share booking details - Opens the device share sheet with the booking reference, status, schedule, service count and total.</t>
+          <t xml:space="preserve">Home screen logo centred correctly - The logo now sits in the true middle of the header whatever the city name is.</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking cancellation and reschedule controls - Cancel uses an in-app confirmation; reschedule is offered only for pending or confirmed bookings, and rescheduled bookings have a visible badge.</t>
+          <t xml:space="preserve">Whole-rupee amounts across all screens - All prices and totals shown in whole rupees.</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add-service confirmation on booking details - Shows an in-app success message with the number of services added and the updated booking total.</t>
+          <t xml:space="preserve">Cart shortcut in bottom navigation - Open checkout directly from the Cart button, with a badge showing the number of selected items.</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimum booking amount enforced - Checkout requires a Rs. 500 subtotal and shows how much more must be added before booking can continue.</t>
+          <t xml:space="preserve">Services, combos and packages in one cart - Checkout handles multiple packages and individual services together, with independent package quantities and correctly calculated extras.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking-time validation - Checks the advance booking buffer and service hours of 8 AM to 8 PM; the default slot moves to next-day opening when the advance buffer passes closing.</t>
+          <t xml:space="preserve">Add More Services from checkout - Returns to Home so customers can add services, combos or packages and come back with their selections retained.</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checkout address restricted to the selected city - Only a matching-city default address is selected; switching city clears an address belonging to another city.</t>
+          <t xml:space="preserve">Checkout state reset for a different package - Reopening checkout with another package refreshes its services, quantities and offer state instead of retaining the previous package selections.</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service quantity limit in checkout - Service quantities are capped at five in checkout controls.</t>
+          <t xml:space="preserve">Service offer prices throughout the app - Home cards, service lists, cart, checkout and booking details show the discounted price, crossed-out original price and percentage off.</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Most Booked service details - Home cards open a service details sheet; customers can dismiss it by swiping down on the handle.</t>
+          <t xml:space="preserve">Removed service offers refresh automatically - Service screens and checkout recheck offers, restore normal prices and update cart totals with an in-app notice when an offer is no longer available; prices are checked again before payment.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home navigation and search improvements - View All Services is available whenever categories exist, and search includes categories, services, packages and offers.</t>
+          <t xml:space="preserve">Free-service offer eligibility rechecked - Removing qualifying paid services clears an ineligible free item; eligibility is checked again before booking submission.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Missing-image placeholders on Home - Most Booked services and package/combo banners display a No image found placeholder when no image is supplied.</t>
+          <t xml:space="preserve">Download and view booking invoices - Generates a PDF invoice from booking data, saves it on the device and provides a View Invoice action with clear success or failure feedback.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package and combo layout improvements - Loading indicators are centred and Book Now aligns at the bottom of combo cards with different service counts.</t>
+          <t xml:space="preserve">Share booking details - Opens the device share sheet with the booking reference, status, schedule, service count and total.</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer notifications fixed - The notification list and unread count now read the API response correctly instead of showing an empty list.</t>
+          <t xml:space="preserve">Booking cancellation and reschedule controls - Cancel uses an in-app confirmation; reschedule is offered only for pending or confirmed bookings, and rescheduled bookings have a visible badge.</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">My Reviews crash fixed - Review cards read nested service and partner details correctly and display their names and images.</t>
+          <t xml:space="preserve">Add-service confirmation on booking details - Shows an in-app success message with the number of services added and the updated booking total.</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Address form keyboard handling on iOS - The address form adjusts and scrolls while typing so the keyboard does not cover the fields.</t>
+          <t xml:space="preserve">Minimum booking amount enforced - Checkout requires a Rs. 500 subtotal and shows how much more must be added before booking can continue.</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automatic city detection on every page - The location is worked out as soon as the site opens, so landing directly on Products or Checkout works correctly - earlier only the home page had a city.</t>
+          <t xml:space="preserve">Booking-time validation - Checks the advance booking buffer and service hours of 8 AM to 8 PM; the default slot moves to next-day opening when the advance buffer passes closing.</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">City-wise services and pricing - Services, categories, packages and prices shown are the ones offered in the selected city.</t>
+          <t xml:space="preserve">Checkout address restricted to the selected city - Only a matching-city default address is selected; switching city clears an address belonging to another city.</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change-city confirmation - Warns before clearing the cart when switching to another city.</t>
+          <t xml:space="preserve">Service quantity limit in checkout - Service quantities are capped at five in checkout controls.</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saved city checked on load - A city that is no longer served is not reused; the site re-detects the location instead of getting stuck.</t>
+          <t xml:space="preserve">Most Booked service details - Home cards open a service details sheet; customers can dismiss it by swiping down on the handle.</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subcategory filter chips on Products - For example Waxing - Honey / Rica / Brazilian, with an 'All' chip to clear the filter, same as the app.</t>
+          <t xml:space="preserve">Home navigation and search improvements - View All Services is available whenever categories exist, and search includes categories, services, packages and offers.</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service start code on booking details - The 4-digit code the customer shares with the expert to start the service.</t>
+          <t xml:space="preserve">Missing-image placeholders on Home - Most Booked services and package/combo banners display a No image found placeholder when no image is supplied.</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">'No image found' placeholder - Services without a picture now show a clean placeholder instead of a broken image.</t>
+          <t xml:space="preserve">Package and combo layout improvements - Loading indicators are centred and Book Now aligns at the bottom of combo cards with different service counts.</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Featured service images in Special Offers - Admin-featured services on the home page now show their images.</t>
+          <t xml:space="preserve">Customer notifications fixed - The notification list and unread count now read the API response correctly instead of showing an empty list.</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimum booking amount message on checkout - Clearly shows how much more needs to be added to reach the minimum booking value.</t>
+          <t xml:space="preserve">My Reviews crash fixed - Review cards read nested service and partner details correctly and display their names and images.</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cart cleared on logout - The cart no longer carries over to the next person signing in on the same browser.</t>
+          <t xml:space="preserve">Address form keyboard handling on iOS - The address form adjusts and scrolls while typing so the keyboard does not cover the fields.</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book Now button on special combo packages - Combo packages are booked from the card's Book Now button instead of clicking anywhere on the card.</t>
+          <t xml:space="preserve">iOS guest browsing - Customers can browse Home, services and the cart without signing in; Android retains its existing login behavior.</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking recorded against the correct city - An order placed for an address in another city is no longer filed under the wrong city.</t>
+          <t xml:space="preserve">iOS login at protected actions - Account-only screens and placing a booking require authentication; logging in from checkout returns to checkout with cart and checkout details retained.</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login and profile popups improved - They now open above all page content, close with the Escape key and lock the background from scrolling.</t>
+          <t xml:space="preserve">Guest profile experience on iOS - Profile displays Login / Register and hides cached account details and booking counts until the customer signs in.</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whole-rupee amounts across the website - All prices, bills and booking totals match the apps and the admin dashboard.</t>
+          <t xml:space="preserve">Customer profile session isolation - Cached profile data resets on login, logout and account deletion, late profile requests from a previous session are ignored, and Profile reloads when authentication changes.</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service offer pricing across the website - Home featured services, Products, Services, cart and checkout show the valid offer price, crossed-out original price and percentage off; line amounts scale with quantity.</t>
+          <t xml:space="preserve">Missing-address feedback in checkout - Continue displays an in-app Address Required message when no address is selected instead of leaving the button disabled without an explanation.</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offer-price validation - Only a finite, positive offer price below the regular price is applied; invalid offer values fall back to regular pricing.</t>
+          <t xml:space="preserve">Notification taps open booking details - Booking notifications retain their booking data and open the corresponding Booking Detail screen after startup/login is ready; duplicate taps are ignored.</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automatic expired-offer checks - Cart offers are checked on page navigation, every 30 seconds while visible, and when the browser regains focus or visibility.</t>
+          <t xml:space="preserve">Clearer Add and quantity buttons - Home Most Booked cards and service listings use green buttons with white labels, icons and quantity counts.</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed-offer notification and cart updates - If a service offer is removed, its normal price is restored, cart totals update and an Offer no longer available message identifies the affected services.</t>
+          <t xml:space="preserve">Home combo banner and header display updated - Combo banner images fill their image area using stretch sizing, and the Home header no longer has rounded lower corners.</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
+          <t xml:space="preserve">Customer App</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offer validation before placing an order - Checkout rechecks service offers before submission; changed prices require the customer to review the updated total, and verification failures display an error.</t>
+          <t xml:space="preserve">Customer Android build version updated - Current versionName is 1.1.8 and versionCode is 18.</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offer-price changes synced to service cards - Home, Products and Services listings receive refreshed pricing when a removed offer updates the cart.</t>
+          <t xml:space="preserve">Automatic city detection on every page - The location is worked out as soon as the site opens, so landing directly on Products or Checkout works correctly - earlier only the home page had a city.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saved-cart price refresh - Existing individual-service cart lines refresh from the service catalog on load, including carts saved before offer-price display was introduced.</t>
+          <t xml:space="preserve">City-wise services and pricing - Services, categories, packages and prices shown are the ones offered in the selected city.</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unavailable-service recovery at checkout - Deactivated individual services are removed while keeping unaffected items; the cart is cleared when an unavailable service is inside a package or cannot be identified, with an explanatory modal.</t>
+          <t xml:space="preserve">Change-city confirmation - Warns before clearing the cart when switching to another city.</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Separate website service descriptions - Products and Services display the website-specific description configured by admin.</t>
+          <t xml:space="preserve">Saved city checked on load - A city that is no longer served is not reused; the site re-detects the location instead of getting stuck.</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subcategory browsing cards - Products shows subcategory image/name cards before the service list, with a back control and a list filtered to the selected subcategory.</t>
+          <t xml:space="preserve">Subcategory filter chips on Products - For example Waxing - Honey / Rica / Brazilian, with an 'All' chip to clear the filter, same as the app.</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cart savings feedback - Updating service selections displays a cart confirmation or savings message calculated from discounted prices.</t>
+          <t xml:space="preserve">Service start code on booking details - The 4-digit code the customer shares with the expert to start the service.</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Missing-image placeholders for package banners - Home package/combo promotions show No image found when admin has not supplied a banner image.</t>
+          <t xml:space="preserve">'No image found' placeholder - Services without a picture now show a clean placeholder instead of a broken image.</t>
         </is>
       </c>
     </row>
@@ -2084,11 +2084,402 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Featured service images in Special Offers - Admin-featured services on the home page now show their images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum booking amount message on checkout - Clearly shows how much more needs to be added to reach the minimum booking value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cart cleared on logout - The cart no longer carries over to the next person signing in on the same browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Book Now button on special combo packages - Combo packages are booked from the card's Book Now button instead of clicking anywhere on the card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Booking recorded against the correct city - An order placed for an address in another city is no longer filed under the wrong city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Login and profile popups improved - They now open above all page content, close with the Escape key and lock the background from scrolling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whole-rupee amounts across the website - All prices, bills and booking totals match the apps and the admin dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service offer pricing across the website - Home featured services, Products, Services, cart and checkout show the valid offer price, crossed-out original price and percentage off; line amounts scale with quantity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offer-price validation - Only a finite, positive offer price below the regular price is applied; invalid offer values fall back to regular pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic expired-offer checks - Cart offers are checked on page navigation, every 30 seconds while visible, and when the browser regains focus or visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed-offer notification and cart updates - If a service offer is removed, its normal price is restored, cart totals update and an Offer no longer available message identifies the affected services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offer validation before placing an order - Checkout rechecks service offers before submission; changed prices require the customer to review the updated total, and verification failures display an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offer-price changes synced to service cards - Home, Products and Services listings receive refreshed pricing when a removed offer updates the cart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saved-cart price refresh - Existing individual-service cart lines refresh from the service catalog on load, including carts saved before offer-price display was introduced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unavailable-service recovery at checkout - Deactivated individual services are removed while keeping unaffected items; the cart is cleared when an unavailable service is inside a package or cannot be identified, with an explanatory modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Separate website service descriptions - Products and Services display the website-specific description configured by admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subcategory browsing cards - Products shows subcategory image/name cards before the service list, with a back control and a list filtered to the selected subcategory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cart savings feedback - Updating service selections displays a cart confirmation or savings message calculated from discounted prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Missing-image placeholders for package banners - Home package/combo promotions show No image found when admin has not supplied a banner image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Banner display improvements - Banner images use contain sizing and a matching background so the full image remains visible without cropping.</t>
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Special Offers service navigation corrected - Clicking a featured service opens its matching category and service, clears unrelated subcategory/combo selections and scrolls to the service once loading finishes; repeated navigation refreshes the target selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated Add and quantity buttons on Products - Service Add buttons and quantity controls use green backgrounds with white labels and counts, with darker hover/pressed styling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum service amount clarified at checkout - The checkout warning and order validation explain that the Rs. 500 minimum applies to the service subtotal excluding GST, and show the current subtotal and additional service amount required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Working iOS App Store download links - Customer app badges in the header, footer and Home link to the Beyomo App Store listing; the Downloads page opens the correct customer and partner App Store listings instead of placeholder links.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C118"/>
+  <autoFilter ref="A1:C141"/>
 </worksheet>
 </file>